--- a/feat/container-mode/ig/StructureDefinition-pdsm-simplified-publish.xlsx
+++ b/feat/container-mode/ig/StructureDefinition-pdsm-simplified-publish.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:13:25+00:00</t>
+    <t>2026-06-30T13:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
